--- a/request_forms/011_deal_memo_submission--request_forms.xlsx
+++ b/request_forms/011_deal_memo_submission--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -845,29 +845,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accurate_and_complete</t>
+          <t>accurate_representation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>accurate and complete</t>
+          <t>accurate representation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>deal_terms_choices</t>
+          <t>deal_acknowledgments_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>accurate_representation</t>
+          <t>acceptance_of_this_submission_constitutes_an_agreement_that_the_deal_details_are_accurate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>accurate representation</t>
+          <t>Acceptance of this submission constitutes an agreement that the deal details are accurate</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>acceptance_of_this_submission_constitutes_an_agreement_that_the_deal_details_are_accurate</t>
+          <t>accurate_and_complete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Acceptance of this submission constitutes an agreement that the deal details are accurate</t>
+          <t>accurate and complete</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>accurate_and_complete</t>
+          <t>i_have_not_altered_the_deal_details_in_any_way</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>accurate and complete</t>
+          <t>I have not altered the deal details in any way</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>i_have_not_altered_the_deal_details_in_any_way</t>
+          <t>this_submission_represents_an_accurate_representation_of_the_deal_details</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>I have not altered the deal details in any way</t>
+          <t>This submission represents an accurate representation of the deal details</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>this_submission_represents_an_accurate_representation_of_the_deal_details</t>
+          <t>this_submission_is_an_accurate_representation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>This submission represents an accurate representation of the deal details</t>
+          <t>This submission is an accurate representation</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>this_submission_is_an_accurate_representation</t>
+          <t>this_is_an_accurate_representation_of_the_deal_details</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>This submission is an accurate representation</t>
+          <t>This is an accurate representation of the deal details</t>
         </is>
       </c>
     </row>
@@ -964,46 +964,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>this_is_an_accurate_representation_of_the_deal_details</t>
+          <t>i_have_not_altered</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>This is an accurate representation of the deal details</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>deal_acknowledgments_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>i_have_not_altered</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>I have not altered</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>deal_acknowledgments_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>accurate_and_complete</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>accurate and complete</t>
         </is>
       </c>
     </row>
